--- a/outputs/53383.xlsx
+++ b/outputs/53383.xlsx
@@ -140,12 +140,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -341,61 +345,61 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
+      <c r="A8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -416,73 +420,73 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="99.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="99.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="0" t="str">
-        <f aca="false">IF(COUNTIFS('worksheet 1'!$A$3:$A$6,$A3,'worksheet 1'!$B$3:$B$6,$B3)&gt;0,"Matched","Not Matched")</f>
+      <c r="C3" s="1" t="str">
+        <f aca="false">IF(VLOOKUP(A3,'worksheet 1'!$A$3:$B$6,2,FALSE())=B3,"Matched","Not Matched")</f>
         <v>Matched</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="str">
-        <f aca="false">IF(COUNTIFS('worksheet 1'!$A$3:$A$6,$A4,'worksheet 1'!$B$3:$B$6,$B4)&gt;0,"Matched","Not Matched")</f>
+      <c r="C4" s="1" t="str">
+        <f aca="false">IF(VLOOKUP(A4,'worksheet 1'!$A$3:$B$6,2,FALSE())=B4,"Matched","Not Matched")</f>
         <v>Not Matched</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="0" t="str">
-        <f aca="false">IF(COUNTIFS('worksheet 1'!$A$3:$A$6,$A5,'worksheet 1'!$B$3:$B$6,$B5)&gt;0,"Matched","Not Matched")</f>
+      <c r="C5" s="1" t="str">
+        <f aca="false">IF(VLOOKUP(A5,'worksheet 1'!$A$3:$B$6,2,FALSE())=B5,"Matched","Not Matched")</f>
         <v>Matched</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="0" t="str">
-        <f aca="false">IF(COUNTIFS('worksheet 1'!$A$3:$A$6,$A6,'worksheet 1'!$B$3:$B$6,$B6)&gt;0,"Matched","Not Matched")</f>
+      <c r="C6" s="1" t="str">
+        <f aca="false">IF(VLOOKUP(A6,'worksheet 1'!$A$3:$B$6,2,FALSE())=B6,"Matched","Not Matched")</f>
         <v>Matched</v>
       </c>
     </row>

--- a/outputs/53383.xlsx
+++ b/outputs/53383.xlsx
@@ -349,12 +349,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -362,7 +362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -370,7 +370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -378,7 +378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -386,7 +386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
     </row>
@@ -426,12 +426,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="99.43"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -442,7 +442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -450,11 +450,11 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="str">
-        <f aca="false">IF(VLOOKUP(A3,'worksheet 1'!$A$3:$B$6,2,FALSE())=B3,"Matched","Not Matched")</f>
+        <f aca="false">IF(AND('worksheet 1'!A3=A3, 'worksheet 1'!B3=B3), "Matched", "Not Matched")</f>
         <v>Matched</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -462,11 +462,11 @@
         <v>8</v>
       </c>
       <c r="C4" s="1" t="str">
-        <f aca="false">IF(VLOOKUP(A4,'worksheet 1'!$A$3:$B$6,2,FALSE())=B4,"Matched","Not Matched")</f>
+        <f aca="false">IF(AND('worksheet 1'!A4=A4, 'worksheet 1'!B4=B4), "Matched", "Not Matched")</f>
         <v>Not Matched</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -474,11 +474,11 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="str">
-        <f aca="false">IF(VLOOKUP(A5,'worksheet 1'!$A$3:$B$6,2,FALSE())=B5,"Matched","Not Matched")</f>
+        <f aca="false">IF(AND('worksheet 1'!A5=A5, 'worksheet 1'!B5=B5), "Matched", "Not Matched")</f>
         <v>Matched</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -486,7 +486,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="1" t="str">
-        <f aca="false">IF(VLOOKUP(A6,'worksheet 1'!$A$3:$B$6,2,FALSE())=B6,"Matched","Not Matched")</f>
+        <f aca="false">IF(AND('worksheet 1'!A6=A6, 'worksheet 1'!B6=B6), "Matched", "Not Matched")</f>
         <v>Matched</v>
       </c>
     </row>
